--- a/request_forms/006_fingerprinting_quote_request_form--request_forms.xlsx
+++ b/request_forms/006_fingerprinting_quote_request_form--request_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1309,8 +1309,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'option':_'fingerprinting'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'option': 'Fingerprinting'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1389,12 +1389,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'option':_'non-fingerprinting'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'option': 'Non-Fingerprinting'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1406,12 +1406,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'option':_'downtown'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'option': 'Downtown'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1423,12 +1423,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'option':_'uptown'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'option': 'Uptown'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1440,12 +1440,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'option':_'other_(please_specify)'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'option': 'Other (please specify)'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1457,12 +1457,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'option':_'service_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'option': 'Service 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1474,12 +1474,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'option':_'service_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'option': 'Service 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1491,12 +1491,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'option':_'service_3'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'option': 'Service 3'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1508,12 +1508,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'option':_'service_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'option': 'Service 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'option':_'service_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'option': 'Service 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1542,12 +1542,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'option':_'service_3'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'option': 'Service 3'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1593,12 +1593,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'option':_true}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'option': True}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1610,12 +1610,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'option':_false}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'option': False}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
